--- a/Inventaire du laboratoire de physique-chimie.xlsx
+++ b/Inventaire du laboratoire de physique-chimie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vince\Travail\Labo\0_LABORATOIRE_RESEAU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\Travail\Labo\0_LABORATOIRE_RESEAU\Inventaire du laboratoire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C113D9-201E-4290-81CD-3B788674097F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70470CC-7CF6-42D5-9CAA-A3B80395D089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D101" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,6 @@
     <sheet name="Produits chimiques" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5666" uniqueCount="2015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="2020">
   <si>
     <t>Inventaire du matériel dans la salle D101</t>
   </si>
@@ -5846,9 +5845,6 @@
     <t>cuves rhéographiques (MEP)</t>
   </si>
   <si>
-    <t xml:space="preserve">   "      "        "    Rx ?????</t>
-  </si>
-  <si>
     <t xml:space="preserve">    "      "       "    Rx10000-7mA</t>
   </si>
   <si>
@@ -6081,13 +6077,49 @@
   </si>
   <si>
     <t>Frigo C105</t>
+  </si>
+  <si>
+    <t>Lunette astronomique</t>
+  </si>
+  <si>
+    <t>Armoire D101 - A</t>
+  </si>
+  <si>
+    <t>Optique</t>
+  </si>
+  <si>
+    <t>Vase de Mariotte</t>
+  </si>
+  <si>
+    <t>Sphère de Pascal</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   "      "        "    Rx k</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ω</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/100</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6188,6 +6220,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -6754,14 +6791,26 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6772,14 +6821,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6790,29 +6842,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9823,8 +9860,8 @@
       <xdr:rowOff>45484</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="45719" cy="264560"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="ZoneTexte 2">
@@ -9869,10 +9906,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="fr-FR" sz="1100" i="1">
                         <a:latin typeface="Cambria Math"/>
@@ -9887,7 +9921,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="ZoneTexte 2">
@@ -9978,8 +10012,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0964DE04-A464-4ADD-BC3D-A26CF0A97D1C}" name="Tableau6" displayName="Tableau6" ref="A3:F660" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
-  <autoFilter ref="A3:F660" xr:uid="{0964DE04-A464-4ADD-BC3D-A26CF0A97D1C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0964DE04-A464-4ADD-BC3D-A26CF0A97D1C}" name="Tableau6" displayName="Tableau6" ref="A3:F662" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
+  <autoFilter ref="A3:F662" xr:uid="{0964DE04-A464-4ADD-BC3D-A26CF0A97D1C}"/>
   <tableColumns count="6">
     <tableColumn id="2" xr3:uid="{F42773BF-2C54-47EC-87D0-205B538A5AE0}" name="Désignation du matériel" dataDxfId="96"/>
     <tableColumn id="3" xr3:uid="{78BBA9E6-CB04-473D-B15F-DDB0F0CF0F61}" name="Quantité" dataDxfId="95"/>
@@ -10374,14 +10408,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="77"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="94"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I2" s="1" t="s">
@@ -10409,6 +10443,18 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2015</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>2016</v>
+      </c>
       <c r="F4" s="53"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -11212,14 +11258,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -12163,116 +12209,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="84"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="86"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="91"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="82" t="s">
         <v>1097</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="80"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="84"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="78" t="s">
-        <v>1976</v>
-      </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
-      <c r="K4" s="80"/>
+      <c r="A4" s="82" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="84"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="82" t="s">
         <v>1098</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="80"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="84"/>
     </row>
     <row r="7" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="85" t="s">
         <v>1099</v>
       </c>
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="85" t="s">
         <v>1100</v>
       </c>
-      <c r="C7" s="91" t="s">
+      <c r="C7" s="85" t="s">
         <v>1101</v>
       </c>
-      <c r="D7" s="91" t="s">
+      <c r="D7" s="85" t="s">
         <v>1102</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="87" t="s">
         <v>1103</v>
       </c>
-      <c r="F7" s="81" t="s">
+      <c r="F7" s="80" t="s">
         <v>1109</v>
       </c>
-      <c r="G7" s="87" t="s">
+      <c r="G7" s="76" t="s">
         <v>1104</v>
       </c>
-      <c r="H7" s="88"/>
-      <c r="I7" s="87" t="s">
+      <c r="H7" s="77"/>
+      <c r="I7" s="76" t="s">
         <v>1105</v>
       </c>
-      <c r="J7" s="88"/>
-      <c r="K7" s="93" t="s">
+      <c r="J7" s="77"/>
+      <c r="K7" s="78" t="s">
         <v>1106</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="92"/>
-      <c r="B8" s="92"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="82"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="81"/>
       <c r="G8" s="12" t="s">
         <v>1107</v>
       </c>
@@ -12285,7 +12331,7 @@
       <c r="J8" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="K8" s="94"/>
+      <c r="K8" s="79"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
@@ -12299,7 +12345,7 @@
         <v>1112</v>
       </c>
       <c r="E9" s="44" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>1107</v>
@@ -12315,7 +12361,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>1111</v>
@@ -12343,7 +12389,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>1111</v>
@@ -12353,7 +12399,7 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="44" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>1107</v>
@@ -12491,7 +12537,7 @@
         <v>1112</v>
       </c>
       <c r="E16" s="44" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>1107</v>
@@ -12601,7 +12647,7 @@
         <v>1136</v>
       </c>
       <c r="E20" s="44" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>1107</v>
@@ -13065,7 +13111,7 @@
         <v>1173</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="G37" s="8" t="s">
         <v>1107</v>
@@ -13093,7 +13139,7 @@
         <v>1176</v>
       </c>
       <c r="E38" s="45" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="G38" s="8" t="s">
         <v>1107</v>
@@ -13121,7 +13167,7 @@
         <v>1176</v>
       </c>
       <c r="E39" s="45" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="G39" s="8" t="s">
         <v>1107</v>
@@ -14301,7 +14347,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
         <v>1255</v>
       </c>
@@ -14327,7 +14373,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>1258</v>
       </c>
@@ -14353,7 +14399,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>1259</v>
       </c>
@@ -14379,7 +14425,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>1261</v>
       </c>
@@ -14407,7 +14453,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
         <v>1261</v>
       </c>
@@ -14433,7 +14479,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
         <v>1263</v>
       </c>
@@ -14461,7 +14507,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A89" s="5" t="s">
         <v>1265</v>
       </c>
@@ -14473,7 +14519,7 @@
         <v>1266</v>
       </c>
       <c r="E89" s="45" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>1107</v>
@@ -14487,7 +14533,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>1268</v>
       </c>
@@ -14513,7 +14559,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
         <v>1269</v>
       </c>
@@ -14539,7 +14585,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
         <v>1270</v>
       </c>
@@ -14551,7 +14597,7 @@
         <v>1266</v>
       </c>
       <c r="E92" s="45" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>1107</v>
@@ -14565,7 +14611,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A93" s="8" t="s">
         <v>1271</v>
       </c>
@@ -14591,7 +14637,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
         <v>1272</v>
       </c>
@@ -14617,7 +14663,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>1274</v>
       </c>
@@ -14643,7 +14689,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="8" t="s">
         <v>1276</v>
       </c>
@@ -14669,7 +14715,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
         <v>1278</v>
       </c>
@@ -14695,7 +14741,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
         <v>1280</v>
       </c>
@@ -14721,7 +14767,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>1283</v>
       </c>
@@ -14747,7 +14793,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
         <v>1285</v>
       </c>
@@ -14773,7 +14819,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
         <v>1288</v>
       </c>
@@ -14799,7 +14845,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>1290</v>
       </c>
@@ -14825,7 +14871,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>1292</v>
       </c>
@@ -14851,7 +14897,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>1294</v>
       </c>
@@ -14877,7 +14923,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>1296</v>
       </c>
@@ -14903,7 +14949,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>1297</v>
       </c>
@@ -14929,7 +14975,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>1299</v>
       </c>
@@ -14983,7 +15029,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>1303</v>
       </c>
@@ -15009,7 +15055,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>1305</v>
       </c>
@@ -15037,7 +15083,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>1307</v>
       </c>
@@ -15065,7 +15111,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>1308</v>
       </c>
@@ -15093,7 +15139,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>1310</v>
       </c>
@@ -15121,7 +15167,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
         <v>1312</v>
       </c>
@@ -15149,7 +15195,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
         <v>1314</v>
       </c>
@@ -15175,7 +15221,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>1315</v>
       </c>
@@ -15203,7 +15249,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
         <v>1318</v>
       </c>
@@ -15231,7 +15277,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
         <v>1320</v>
       </c>
@@ -15287,7 +15333,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
         <v>1324</v>
       </c>
@@ -15315,7 +15361,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>1325</v>
       </c>
@@ -15343,7 +15389,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>1327</v>
       </c>
@@ -15371,7 +15417,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>1328</v>
       </c>
@@ -15399,7 +15445,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>1330</v>
       </c>
@@ -15425,7 +15471,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>1331</v>
       </c>
@@ -15451,7 +15497,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>1334</v>
       </c>
@@ -15477,7 +15523,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>1336</v>
       </c>
@@ -15585,7 +15631,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B131" s="8" t="s">
         <v>1149</v>
@@ -15787,7 +15833,7 @@
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="45" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="G138" s="8" t="s">
         <v>1107</v>
@@ -15813,7 +15859,7 @@
       </c>
       <c r="D139" s="5"/>
       <c r="E139" s="45" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="G139" s="8" t="s">
         <v>1107</v>
@@ -16625,7 +16671,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A172" s="8" t="s">
         <v>1418</v>
       </c>
@@ -16649,7 +16695,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A173" s="8" t="s">
         <v>1419</v>
       </c>
@@ -16673,7 +16719,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>1420</v>
       </c>
@@ -16685,7 +16731,7 @@
         <v>1256</v>
       </c>
       <c r="E174" s="44" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="G174" s="8" t="s">
         <v>1107</v>
@@ -16699,7 +16745,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>1278</v>
       </c>
@@ -16725,7 +16771,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>1424</v>
       </c>
@@ -16739,7 +16785,7 @@
         <v>1427</v>
       </c>
       <c r="E176" s="44" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>1107</v>
@@ -16753,7 +16799,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>1425</v>
       </c>
@@ -16785,7 +16831,7 @@
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="25" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="D178" s="8"/>
       <c r="E178" s="44"/>
@@ -16797,7 +16843,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B179" s="8" t="s">
         <v>1149</v>
@@ -16827,7 +16873,7 @@
       </c>
       <c r="D180" s="8"/>
       <c r="E180" s="44" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="G180" s="8" t="s">
         <v>1107</v>
@@ -16873,7 +16919,7 @@
       </c>
       <c r="D182" s="8"/>
       <c r="E182" s="44" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>1107</v>
@@ -16887,7 +16933,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="8" t="s">
         <v>1435</v>
       </c>
@@ -16915,7 +16961,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="8" t="s">
         <v>1436</v>
       </c>
@@ -16924,7 +16970,7 @@
       </c>
       <c r="C184" s="25"/>
       <c r="D184" s="8" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="E184" s="44" t="s">
         <v>1444</v>
@@ -16941,7 +16987,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="8" t="s">
         <v>1439</v>
       </c>
@@ -16953,7 +16999,7 @@
         <v>1440</v>
       </c>
       <c r="E185" s="44" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="G185" s="8" t="s">
         <v>1107</v>
@@ -16967,7 +17013,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="8" t="s">
         <v>1441</v>
       </c>
@@ -16993,7 +17039,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="8" t="s">
         <v>1442</v>
       </c>
@@ -17019,7 +17065,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="8" t="s">
         <v>1443</v>
       </c>
@@ -17045,7 +17091,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="8" t="s">
         <v>1445</v>
       </c>
@@ -17054,7 +17100,7 @@
       </c>
       <c r="C189" s="25"/>
       <c r="D189" s="8" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="E189" s="44">
         <v>0</v>
@@ -17071,7 +17117,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" s="8" t="s">
         <v>1447</v>
       </c>
@@ -17097,7 +17143,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="8" t="s">
         <v>1449</v>
       </c>
@@ -17123,7 +17169,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="8" t="s">
         <v>1450</v>
       </c>
@@ -17149,7 +17195,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="25"/>
@@ -17163,7 +17209,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
       <c r="C194" s="26"/>
@@ -17201,7 +17247,7 @@
       <c r="J195" s="8"/>
       <c r="K195" s="8"/>
     </row>
-    <row r="196" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="8" t="s">
         <v>1453</v>
       </c>
@@ -17269,7 +17315,7 @@
         <v>1151</v>
       </c>
       <c r="E198" s="44" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="G198" s="8" t="s">
         <v>1107</v>
@@ -17299,7 +17345,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" s="8" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>1149</v>
@@ -17389,7 +17435,7 @@
         <v>1459</v>
       </c>
       <c r="E203" s="44" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="G203" s="8" t="s">
         <v>1107</v>
@@ -17417,7 +17463,7 @@
         <v>1459</v>
       </c>
       <c r="E204" s="44" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="G204" s="8" t="s">
         <v>1107</v>
@@ -17843,7 +17889,7 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="8" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B220" s="8" t="s">
         <v>1111</v>
@@ -17997,7 +18043,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" s="8" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B226" s="8" t="s">
         <v>1149</v>
@@ -18070,7 +18116,7 @@
       </c>
       <c r="J228" s="8"/>
       <c r="K228" s="8" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.3">
@@ -18197,13 +18243,13 @@
     </row>
     <row r="234" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A234" s="8" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B234" s="8" t="s">
         <v>1149</v>
       </c>
       <c r="C234" s="13" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="D234" s="8"/>
       <c r="E234" s="45" t="s">
@@ -18387,7 +18433,7 @@
         <v>1507</v>
       </c>
       <c r="E241" s="45" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>1107</v>
@@ -18587,7 +18633,7 @@
       <c r="C249" s="13"/>
       <c r="D249" s="8"/>
       <c r="E249" s="45" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="G249" s="8" t="s">
         <v>1107</v>
@@ -18623,7 +18669,7 @@
         <v>1149</v>
       </c>
       <c r="C251" s="13" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="D251" s="8"/>
       <c r="E251" s="45" t="s">
@@ -18783,7 +18829,7 @@
         <v>1149</v>
       </c>
       <c r="C257" s="28" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D257" s="5" t="s">
         <v>1133</v>
@@ -18805,7 +18851,7 @@
     </row>
     <row r="258" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A258" s="5" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B258" s="8" t="s">
         <v>1149</v>
@@ -19075,7 +19121,7 @@
         <v>1545</v>
       </c>
       <c r="E268" s="44" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="G268" s="8" t="s">
         <v>1107</v>
@@ -19097,7 +19143,7 @@
         <v>1149</v>
       </c>
       <c r="C269" s="25" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="D269" s="5"/>
       <c r="E269" s="44" t="s">
@@ -19251,7 +19297,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="8" t="s">
         <v>1558</v>
       </c>
@@ -19279,7 +19325,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" s="8" t="s">
         <v>1560</v>
       </c>
@@ -19305,7 +19351,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="8" t="s">
         <v>1562</v>
       </c>
@@ -19355,7 +19401,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A279" s="8" t="s">
         <v>1278</v>
       </c>
@@ -19381,7 +19427,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A280" s="8" t="s">
         <v>1566</v>
       </c>
@@ -19421,7 +19467,7 @@
       </c>
       <c r="D281" s="8"/>
       <c r="E281" s="45" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="G281" s="8" t="s">
         <v>1107</v>
@@ -19499,7 +19545,7 @@
       </c>
       <c r="D284" s="8"/>
       <c r="E284" s="45" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="G284" s="8" t="s">
         <v>1107</v>
@@ -20517,7 +20563,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66C8ACF-0CD6-4AAD-BCF4-57ED61DB99C2}">
   <sheetPr codeName="Feuil2"/>
-  <dimension ref="A1:F660"/>
+  <dimension ref="A1:F662"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="50.109375" style="2" bestFit="1" customWidth="1"/>
@@ -20530,14 +20576,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -20966,30 +21012,26 @@
       </c>
       <c r="F27" s="71"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>597</v>
+        <v>2018</v>
       </c>
       <c r="B28" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="71" t="s">
-        <v>598</v>
-      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="71"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B29" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>561</v>
@@ -20997,19 +21039,17 @@
       <c r="D29" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>600</v>
-      </c>
+      <c r="E29" s="3"/>
       <c r="F29" s="71" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>561</v>
@@ -21018,16 +21058,18 @@
         <v>589</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="F30" s="71"/>
+        <v>600</v>
+      </c>
+      <c r="F30" s="71" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B31" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>561</v>
@@ -21036,18 +21078,16 @@
         <v>589</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="F31" s="71" t="s">
-        <v>605</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="F31" s="71"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B32" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>561</v>
@@ -21056,16 +21096,18 @@
         <v>589</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="F32" s="71"/>
+        <v>604</v>
+      </c>
+      <c r="F32" s="71" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>561</v>
@@ -21074,13 +21116,13 @@
         <v>589</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>502</v>
+        <v>594</v>
       </c>
       <c r="F33" s="71"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B34" s="3">
         <v>1</v>
@@ -21094,19 +21136,17 @@
       <c r="E34" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="F34" s="71">
-        <v>42269</v>
-      </c>
+      <c r="F34" s="71"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B35" s="3">
         <v>1</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>610</v>
+        <v>561</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>589</v>
@@ -21120,13 +21160,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B36" s="3">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>561</v>
+        <v>610</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>589</v>
@@ -21139,50 +21179,52 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="71"/>
+      <c r="A37" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B37" s="3">
+        <v>1</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="F37" s="71">
+        <v>42269</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="B38" s="3">
-        <v>18</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>613</v>
-      </c>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="71"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B39" s="3">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>295</v>
-      </c>
+        <v>613</v>
+      </c>
+      <c r="E39" s="3"/>
       <c r="F39" s="71"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B40" s="3">
         <v>8</v>
@@ -21200,16 +21242,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B41" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>295</v>
@@ -21218,10 +21260,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B42" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>567</v>
@@ -21236,10 +21278,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B43" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>567</v>
@@ -21254,10 +21296,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B44" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>567</v>
@@ -21272,10 +21314,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B45" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>567</v>
@@ -21290,7 +21332,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B46" s="3">
         <v>6</v>
@@ -21308,10 +21350,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B47" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>567</v>
@@ -21326,10 +21368,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B48" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>567</v>
@@ -21344,10 +21386,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B49" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>567</v>
@@ -21362,16 +21404,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B50" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>295</v>
@@ -21380,16 +21422,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B51" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>295</v>
@@ -21398,10 +21440,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B52" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>567</v>
@@ -21416,10 +21458,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B53" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>567</v>
@@ -21434,25 +21476,25 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>633</v>
+        <v>618</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>634</v>
+        <v>295</v>
       </c>
       <c r="F54" s="71"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B55" s="3">
         <v>1</v>
@@ -21464,13 +21506,13 @@
         <v>633</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>600</v>
+        <v>634</v>
       </c>
       <c r="F55" s="71"/>
     </row>
-    <row r="56" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>1921</v>
+        <v>635</v>
       </c>
       <c r="B56" s="3">
         <v>1</v>
@@ -21481,11 +21523,14 @@
       <c r="D56" s="3" t="s">
         <v>633</v>
       </c>
+      <c r="E56" s="3" t="s">
+        <v>600</v>
+      </c>
       <c r="F56" s="71"/>
     </row>
     <row r="57" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B57" s="3">
         <v>1</v>
@@ -21498,9 +21543,9 @@
       </c>
       <c r="F57" s="71"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>636</v>
+        <v>1922</v>
       </c>
       <c r="B58" s="3">
         <v>1</v>
@@ -21511,14 +21556,11 @@
       <c r="D58" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>502</v>
-      </c>
       <c r="F58" s="71"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B59" s="3">
         <v>1</v>
@@ -21530,16 +21572,16 @@
         <v>633</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>573</v>
+        <v>502</v>
       </c>
       <c r="F59" s="71"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B60" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>567</v>
@@ -21554,16 +21596,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B61" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>573</v>
@@ -21572,15 +21614,17 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B62" s="3">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>640</v>
+      </c>
       <c r="E62" s="3" t="s">
         <v>573</v>
       </c>
@@ -21588,100 +21632,96 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B63" s="3">
+        <v>30</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="F63" s="71"/>
+    </row>
+    <row r="64" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B64" s="2">
         <v>1</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="F63" s="71"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
-        <v>1923</v>
-      </c>
-      <c r="B64" s="3">
-        <v>9</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>644</v>
-      </c>
+      <c r="E64" s="2"/>
       <c r="F64" s="71"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>1924</v>
+        <v>642</v>
       </c>
       <c r="B65" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>562</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="F65" s="71"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>645</v>
+        <v>1923</v>
       </c>
       <c r="B66" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>646</v>
+        <v>562</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F66" s="71"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>648</v>
+        <v>1924</v>
       </c>
       <c r="B67" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>646</v>
+        <v>562</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F67" s="71"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="5" t="s">
-        <v>649</v>
+      <c r="A68" s="3" t="s">
+        <v>645</v>
       </c>
       <c r="B68" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>567</v>
@@ -21696,52 +21736,52 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B69" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>651</v>
+        <v>567</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="F69" s="71"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="3" t="s">
-        <v>653</v>
+      <c r="A70" s="5" t="s">
+        <v>649</v>
       </c>
       <c r="B70" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="F70" s="71"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B71" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>615</v>
+        <v>502</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>652</v>
@@ -21750,10 +21790,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B72" s="3">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>567</v>
@@ -21768,16 +21808,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B73" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>502</v>
+        <v>615</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>652</v>
@@ -21786,10 +21826,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B74" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>567</v>
@@ -21804,7 +21844,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B75" s="3">
         <v>4</v>
@@ -21822,10 +21862,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B76" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>567</v>
@@ -21840,10 +21880,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B77" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>567</v>
@@ -21858,10 +21898,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B78" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>567</v>
@@ -21876,10 +21916,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>1925</v>
+        <v>660</v>
       </c>
       <c r="B79" s="3">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>567</v>
@@ -21894,16 +21934,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B80" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>618</v>
+        <v>502</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>652</v>
@@ -21912,16 +21952,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>663</v>
+        <v>1925</v>
       </c>
       <c r="B81" s="3">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>567</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>618</v>
+        <v>502</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>652</v>
@@ -21930,10 +21970,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B82" s="3">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>567</v>
@@ -21948,10 +21988,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B83" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>567</v>
@@ -21966,10 +22006,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>1926</v>
+        <v>664</v>
       </c>
       <c r="B84" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>567</v>
@@ -21984,10 +22024,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B85" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>567</v>
@@ -22000,9 +22040,9 @@
       </c>
       <c r="F85" s="71"/>
     </row>
-    <row r="86" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B86" s="3">
         <v>10</v>
@@ -22020,10 +22060,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B87" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>567</v>
@@ -22036,12 +22076,12 @@
       </c>
       <c r="F87" s="71"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>668</v>
+        <v>1927</v>
       </c>
       <c r="B88" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>567</v>
@@ -22056,10 +22096,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B89" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>567</v>
@@ -22074,10 +22114,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B90" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>567</v>
@@ -22092,46 +22132,46 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B91" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>672</v>
+        <v>567</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>536</v>
+        <v>652</v>
       </c>
       <c r="F91" s="71"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B92" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>672</v>
+        <v>567</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>673</v>
+        <v>618</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>502</v>
+        <v>652</v>
       </c>
       <c r="F92" s="71"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>1928</v>
+        <v>671</v>
       </c>
       <c r="B93" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>672</v>
@@ -22140,16 +22180,16 @@
         <v>673</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="F93" s="71"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B94" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>672</v>
@@ -22164,25 +22204,25 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>676</v>
+        <v>1928</v>
       </c>
       <c r="B95" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>673</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="F95" s="71"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B96" s="3">
         <v>8</v>
@@ -22200,13 +22240,13 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B97" s="3">
         <v>10</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>673</v>
@@ -22218,10 +22258,10 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B98" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>672</v>
@@ -22236,10 +22276,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B99" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>672</v>
@@ -22254,10 +22294,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B100" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>672</v>
@@ -22272,10 +22312,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B101" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>672</v>
@@ -22290,10 +22330,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B102" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>672</v>
@@ -22308,10 +22348,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B103" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>672</v>
@@ -22326,10 +22366,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B104" s="3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>672</v>
@@ -22344,10 +22384,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B105" s="3">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>672</v>
@@ -22362,10 +22402,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B106" s="3">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>672</v>
@@ -22380,10 +22420,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>1929</v>
+        <v>687</v>
       </c>
       <c r="B107" s="3">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>672</v>
@@ -22398,10 +22438,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>1930</v>
+        <v>688</v>
       </c>
       <c r="B108" s="3">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>672</v>
@@ -22416,7 +22456,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="B109" s="3">
         <v>25</v>
@@ -22432,9 +22472,9 @@
       </c>
       <c r="F109" s="71"/>
     </row>
-    <row r="110" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="B110" s="3">
         <v>1</v>
@@ -22448,16 +22488,29 @@
       <c r="E110" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="F110" s="71">
-        <v>43776</v>
-      </c>
+      <c r="F110" s="71"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B111" s="3">
+        <v>25</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="F111" s="71"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>689</v>
+        <v>1932</v>
       </c>
       <c r="B112" s="3">
         <v>1</v>
@@ -22469,34 +22522,21 @@
         <v>673</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="F112" s="71"/>
+        <v>502</v>
+      </c>
+      <c r="F112" s="71">
+        <v>43776</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="B113" s="3">
-        <v>1</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>502</v>
-      </c>
       <c r="F113" s="71"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B114" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>672</v>
@@ -22505,16 +22545,16 @@
         <v>673</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>502</v>
+        <v>690</v>
       </c>
       <c r="F114" s="71"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B115" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>672</v>
@@ -22529,10 +22569,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B116" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>672</v>
@@ -22547,10 +22587,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B117" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="s">
         <v>672</v>
@@ -22565,10 +22605,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B118" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118" s="3" t="s">
         <v>672</v>
@@ -22583,7 +22623,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B119" s="3">
         <v>1</v>
@@ -22601,10 +22641,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B120" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>672</v>
@@ -22613,13 +22653,13 @@
         <v>673</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>536</v>
+        <v>502</v>
       </c>
       <c r="F120" s="71"/>
     </row>
-    <row r="121" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>1933</v>
+        <v>697</v>
       </c>
       <c r="B121" s="3">
         <v>1</v>
@@ -22631,16 +22671,16 @@
         <v>673</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>690</v>
+        <v>502</v>
       </c>
       <c r="F121" s="71"/>
     </row>
-    <row r="122" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>1934</v>
+        <v>698</v>
       </c>
       <c r="B122" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>672</v>
@@ -22649,16 +22689,16 @@
         <v>673</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>690</v>
+        <v>536</v>
       </c>
       <c r="F122" s="71"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="5" t="s">
-        <v>699</v>
+    <row r="123" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A123" s="3" t="s">
+        <v>1933</v>
       </c>
       <c r="B123" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>672</v>
@@ -22667,16 +22707,16 @@
         <v>673</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>541</v>
+        <v>690</v>
       </c>
       <c r="F123" s="71"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>700</v>
+        <v>1934</v>
       </c>
       <c r="B124" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>672</v>
@@ -22685,34 +22725,34 @@
         <v>673</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>502</v>
+        <v>690</v>
       </c>
       <c r="F124" s="71"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="3" t="s">
-        <v>701</v>
+      <c r="A125" s="5" t="s">
+        <v>699</v>
       </c>
       <c r="B125" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>702</v>
+        <v>672</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>673</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>703</v>
+        <v>541</v>
       </c>
       <c r="F125" s="71"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B126" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>672</v>
@@ -22727,28 +22767,28 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B127" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>672</v>
+        <v>702</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>673</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>502</v>
+        <v>703</v>
       </c>
       <c r="F127" s="71"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B128" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C128" s="3" t="s">
         <v>672</v>
@@ -22763,10 +22803,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B129" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>672</v>
@@ -22781,10 +22821,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B130" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>672</v>
@@ -22799,10 +22839,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B131" s="3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>672</v>
@@ -22817,10 +22857,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B132" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>672</v>
@@ -22835,10 +22875,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B133" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C133" s="3" t="s">
         <v>672</v>
@@ -22853,10 +22893,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>1936</v>
+        <v>710</v>
       </c>
       <c r="B134" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>672</v>
@@ -22871,10 +22911,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>1937</v>
+        <v>711</v>
       </c>
       <c r="B135" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>672</v>
@@ -22889,44 +22929,46 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>1935</v>
+        <v>2019</v>
       </c>
       <c r="B136" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>713</v>
+        <v>672</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>673</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>644</v>
+        <v>502</v>
       </c>
       <c r="F136" s="71"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>712</v>
+        <v>1936</v>
       </c>
       <c r="B137" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>713</v>
+        <v>672</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="E137" s="3"/>
+      <c r="E137" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="F137" s="71"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>714</v>
+        <v>1935</v>
       </c>
       <c r="B138" s="3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C138" s="3" t="s">
         <v>713</v>
@@ -22934,15 +22976,17 @@
       <c r="D138" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="E138" s="3"/>
+      <c r="E138" s="3" t="s">
+        <v>644</v>
+      </c>
       <c r="F138" s="71"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B139" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>713</v>
@@ -22950,17 +22994,15 @@
       <c r="D139" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="E139" s="3" t="s">
-        <v>716</v>
-      </c>
+      <c r="E139" s="3"/>
       <c r="F139" s="71"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B140" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" s="3" t="s">
         <v>713</v>
@@ -22968,17 +23010,15 @@
       <c r="D140" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="E140" s="3" t="s">
-        <v>718</v>
-      </c>
+      <c r="E140" s="3"/>
       <c r="F140" s="71"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>713</v>
@@ -22986,12 +23026,14 @@
       <c r="D141" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="E141" s="3"/>
+      <c r="E141" s="3" t="s">
+        <v>716</v>
+      </c>
       <c r="F141" s="71"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B142" s="3">
         <v>1</v>
@@ -23003,16 +23045,16 @@
         <v>673</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F142" s="71"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B143" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>713</v>
@@ -23025,7 +23067,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B144" s="3">
         <v>1</v>
@@ -23037,52 +23079,50 @@
         <v>673</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F144" s="71"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B145" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>713</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>726</v>
+        <v>673</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="71"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B146" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>713</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>726</v>
+        <v>673</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="F146" s="71">
-        <v>45261</v>
-      </c>
+        <v>724</v>
+      </c>
+      <c r="F146" s="71"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B147" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>713</v>
@@ -23095,10 +23135,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>713</v>
@@ -23106,60 +23146,64 @@
       <c r="D148" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="E148" s="3"/>
-      <c r="F148" s="71"/>
+      <c r="E148" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="F148" s="71">
+        <v>45261</v>
+      </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="5" t="s">
-        <v>730</v>
+      <c r="A149" s="3" t="s">
+        <v>728</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>713</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>673</v>
+        <v>726</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="71"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="5" t="s">
-        <v>731</v>
+      <c r="A150" s="3" t="s">
+        <v>729</v>
       </c>
       <c r="B150" s="3">
         <v>1</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="D150" s="3"/>
-      <c r="E150" s="3" t="s">
-        <v>644</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="E150" s="3"/>
       <c r="F150" s="71"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="5" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B151" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3" t="s">
-        <v>734</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="E151" s="3"/>
       <c r="F151" s="71"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="5" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B152" s="3">
         <v>1</v>
@@ -23169,68 +23213,64 @@
       </c>
       <c r="D152" s="3"/>
       <c r="E152" s="3" t="s">
-        <v>734</v>
+        <v>644</v>
       </c>
       <c r="F152" s="71"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="B153" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>732</v>
       </c>
       <c r="D153" s="3"/>
       <c r="E153" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="F153" s="71"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="3" t="s">
-        <v>738</v>
+      <c r="A154" s="5" t="s">
+        <v>735</v>
       </c>
       <c r="B154" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="D154" s="3" t="s">
-        <v>726</v>
-      </c>
+      <c r="D154" s="3"/>
       <c r="E154" s="3" t="s">
-        <v>295</v>
+        <v>734</v>
       </c>
       <c r="F154" s="71"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="3" t="s">
-        <v>1938</v>
+      <c r="A155" s="5" t="s">
+        <v>736</v>
       </c>
       <c r="B155" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="D155" s="3" t="s">
-        <v>726</v>
-      </c>
+      <c r="D155" s="3"/>
       <c r="E155" s="3" t="s">
-        <v>295</v>
+        <v>737</v>
       </c>
       <c r="F155" s="71"/>
     </row>
-    <row r="156" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>1939</v>
+        <v>738</v>
       </c>
       <c r="B156" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>732</v>
@@ -23243,12 +23283,12 @@
       </c>
       <c r="F156" s="71"/>
     </row>
-    <row r="157" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>1940</v>
+        <v>1937</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>732</v>
@@ -23257,16 +23297,16 @@
         <v>726</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>1944</v>
+        <v>295</v>
       </c>
       <c r="F157" s="71"/>
     </row>
     <row r="158" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>1941</v>
+        <v>1938</v>
       </c>
       <c r="B158" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C158" s="3" t="s">
         <v>732</v>
@@ -23275,16 +23315,16 @@
         <v>726</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>1944</v>
+        <v>295</v>
       </c>
       <c r="F158" s="71"/>
     </row>
     <row r="159" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>1942</v>
+        <v>1939</v>
       </c>
       <c r="B159" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>732</v>
@@ -23299,7 +23339,7 @@
     </row>
     <row r="160" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="B160" s="3">
         <v>3</v>
@@ -23317,10 +23357,10 @@
     </row>
     <row r="161" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>732</v>
@@ -23329,16 +23369,16 @@
         <v>726</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F161" s="71"/>
     </row>
     <row r="162" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="B162" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>732</v>
@@ -23347,16 +23387,16 @@
         <v>726</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F162" s="71"/>
     </row>
     <row r="163" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>1948</v>
+        <v>1945</v>
       </c>
       <c r="B163" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>732</v>
@@ -23365,16 +23405,16 @@
         <v>726</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F163" s="71"/>
     </row>
     <row r="164" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>1949</v>
+        <v>1946</v>
       </c>
       <c r="B164" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>732</v>
@@ -23383,18 +23423,16 @@
         <v>726</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F164" s="71">
-        <v>44692</v>
-      </c>
+        <v>1942</v>
+      </c>
+      <c r="F164" s="71"/>
     </row>
     <row r="165" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>732</v>
@@ -23403,15 +23441,13 @@
         <v>726</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F165" s="71">
-        <v>44692</v>
-      </c>
+        <v>1942</v>
+      </c>
+      <c r="F165" s="71"/>
     </row>
     <row r="166" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="B166" s="3">
         <v>1</v>
@@ -23423,7 +23459,7 @@
         <v>726</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F166" s="71">
         <v>44692</v>
@@ -23431,7 +23467,7 @@
     </row>
     <row r="167" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>1952</v>
+        <v>1949</v>
       </c>
       <c r="B167" s="3">
         <v>1</v>
@@ -23443,7 +23479,7 @@
         <v>726</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="F167" s="71">
         <v>44692</v>
@@ -23451,10 +23487,10 @@
     </row>
     <row r="168" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>1953</v>
+        <v>1950</v>
       </c>
       <c r="B168" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>732</v>
@@ -23463,13 +23499,15 @@
         <v>726</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F168" s="71"/>
+        <v>1942</v>
+      </c>
+      <c r="F168" s="71">
+        <v>44692</v>
+      </c>
     </row>
     <row r="169" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>1954</v>
+        <v>1951</v>
       </c>
       <c r="B169" s="3">
         <v>1</v>
@@ -23481,54 +23519,54 @@
         <v>726</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>1943</v>
-      </c>
-      <c r="F169" s="71"/>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1942</v>
+      </c>
+      <c r="F169" s="71">
+        <v>44692</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>739</v>
+        <v>1952</v>
       </c>
       <c r="B170" s="3">
+        <v>2</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F170" s="71"/>
+    </row>
+    <row r="171" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B171" s="3">
         <v>1</v>
       </c>
-      <c r="C170" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="F170" s="71">
-        <v>41775</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="B171" s="3">
-        <v>9</v>
-      </c>
       <c r="C171" s="3" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>741</v>
+        <v>726</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>744</v>
+        <v>1942</v>
       </c>
       <c r="F171" s="71"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="B172" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>740</v>
@@ -23536,15 +23574,19 @@
       <c r="D172" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E172" s="3"/>
-      <c r="F172" s="71"/>
+      <c r="E172" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="F172" s="71">
+        <v>41775</v>
+      </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="5" t="s">
-        <v>746</v>
+      <c r="A173" s="3" t="s">
+        <v>743</v>
       </c>
       <c r="B173" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C173" s="3" t="s">
         <v>740</v>
@@ -23552,80 +23594,82 @@
       <c r="D173" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E173" s="3"/>
+      <c r="E173" s="3" t="s">
+        <v>744</v>
+      </c>
       <c r="F173" s="71"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B174" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E174" s="3" t="s">
-        <v>644</v>
-      </c>
+      <c r="E174" s="3"/>
       <c r="F174" s="71"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="3" t="s">
-        <v>748</v>
+      <c r="A175" s="5" t="s">
+        <v>746</v>
       </c>
       <c r="B175" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E175" s="3" t="s">
-        <v>502</v>
-      </c>
+      <c r="E175" s="3"/>
       <c r="F175" s="71"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E176" s="3"/>
+      <c r="E176" s="3" t="s">
+        <v>644</v>
+      </c>
       <c r="F176" s="71"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="5" t="s">
-        <v>750</v>
+      <c r="A177" s="3" t="s">
+        <v>748</v>
       </c>
       <c r="B177" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E177" s="3"/>
+      <c r="E177" s="3" t="s">
+        <v>502</v>
+      </c>
       <c r="F177" s="71"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B178" s="3">
         <v>1</v>
@@ -23640,11 +23684,11 @@
       <c r="F178" s="71"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="3" t="s">
-        <v>752</v>
+      <c r="A179" s="5" t="s">
+        <v>750</v>
       </c>
       <c r="B179" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>740</v>
@@ -23657,10 +23701,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B180" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>740</v>
@@ -23673,7 +23717,7 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B181" s="3">
         <v>1</v>
@@ -23689,10 +23733,10 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C182" s="3" t="s">
         <v>740</v>
@@ -23705,7 +23749,7 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B183" s="3">
         <v>1</v>
@@ -23716,16 +23760,12 @@
       <c r="D183" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E183" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="F183" s="71">
-        <v>41775</v>
-      </c>
+      <c r="E183" s="3"/>
+      <c r="F183" s="71"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B184" s="3">
         <v>1</v>
@@ -23733,16 +23773,18 @@
       <c r="C184" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="D184" s="3"/>
+      <c r="D184" s="3" t="s">
+        <v>741</v>
+      </c>
       <c r="E184" s="3"/>
       <c r="F184" s="71"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B185" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>740</v>
@@ -23750,45 +23792,49 @@
       <c r="D185" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E185" s="3"/>
-      <c r="F185" s="71"/>
+      <c r="E185" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F185" s="71">
+        <v>41775</v>
+      </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="B186" s="3" t="s">
-        <v>588</v>
+        <v>757</v>
+      </c>
+      <c r="B186" s="3">
+        <v>1</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="D186" s="3" t="s">
-        <v>741</v>
-      </c>
+      <c r="D186" s="3"/>
       <c r="E186" s="3"/>
       <c r="F186" s="71"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="B187" s="5">
+      <c r="A187" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="B187" s="3">
         <v>2</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="D187" s="3"/>
+      <c r="D187" s="3" t="s">
+        <v>741</v>
+      </c>
       <c r="E187" s="3"/>
       <c r="F187" s="71"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="5" t="s">
-        <v>761</v>
-      </c>
-      <c r="B188" s="3">
-        <v>1</v>
+      <c r="A188" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>588</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>740</v>
@@ -23796,50 +23842,44 @@
       <c r="D188" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="E188" s="3" t="s">
-        <v>690</v>
-      </c>
+      <c r="E188" s="3"/>
       <c r="F188" s="71"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="B189" s="3">
+      <c r="A189" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="B189" s="5">
         <v>2</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="D189" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>763</v>
-      </c>
+      <c r="D189" s="3"/>
+      <c r="E189" s="3"/>
       <c r="F189" s="71"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B190" s="3">
         <v>1</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="D190" s="3" t="s">
         <v>741</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>763</v>
+        <v>690</v>
       </c>
       <c r="F190" s="71"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="5" t="s">
-        <v>765</v>
+      <c r="A191" s="3" t="s">
+        <v>762</v>
       </c>
       <c r="B191" s="3">
         <v>2</v>
@@ -23856,14 +23896,14 @@
       <c r="F191" s="71"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="3" t="s">
-        <v>766</v>
+      <c r="A192" s="5" t="s">
+        <v>764</v>
       </c>
       <c r="B192" s="3">
         <v>1</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>741</v>
@@ -23874,11 +23914,11 @@
       <c r="F192" s="71"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="3" t="s">
-        <v>767</v>
+      <c r="A193" s="5" t="s">
+        <v>765</v>
       </c>
       <c r="B193" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C193" s="3" t="s">
         <v>740</v>
@@ -23887,16 +23927,16 @@
         <v>741</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>690</v>
+        <v>763</v>
       </c>
       <c r="F193" s="71"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B194" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>740</v>
@@ -23905,18 +23945,16 @@
         <v>741</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="F194" s="71">
-        <v>42491</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="F194" s="71"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B195" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>740</v>
@@ -23930,11 +23968,11 @@
       <c r="F195" s="71"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="5" t="s">
-        <v>770</v>
+      <c r="A196" s="3" t="s">
+        <v>768</v>
       </c>
       <c r="B196" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>740</v>
@@ -23945,14 +23983,16 @@
       <c r="E196" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="F196" s="71"/>
+      <c r="F196" s="71">
+        <v>42491</v>
+      </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197" s="5" t="s">
-        <v>771</v>
+      <c r="A197" s="3" t="s">
+        <v>769</v>
       </c>
       <c r="B197" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>740</v>
@@ -23967,10 +24007,10 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B198" s="3">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>740</v>
@@ -23979,16 +24019,16 @@
         <v>741</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>763</v>
+        <v>690</v>
       </c>
       <c r="F198" s="71"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A199" s="3" t="s">
-        <v>773</v>
+      <c r="A199" s="5" t="s">
+        <v>771</v>
       </c>
       <c r="B199" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>740</v>
@@ -24002,11 +24042,11 @@
       <c r="F199" s="71"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A200" s="3" t="s">
-        <v>774</v>
+      <c r="A200" s="5" t="s">
+        <v>772</v>
       </c>
       <c r="B200" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>740</v>
@@ -24015,22 +24055,22 @@
         <v>741</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>690</v>
+        <v>763</v>
       </c>
       <c r="F200" s="71"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B201" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>740</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>502</v>
+        <v>741</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>690</v>
@@ -24039,16 +24079,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B202" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>740</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>502</v>
+        <v>741</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>690</v>
@@ -24057,10 +24097,10 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B203" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C203" s="3" t="s">
         <v>740</v>
@@ -24075,10 +24115,10 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B204" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>740</v>
@@ -24093,7 +24133,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B205" s="3">
         <v>9</v>
@@ -24110,78 +24150,78 @@
       <c r="F205" s="71"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A206" s="5" t="s">
-        <v>780</v>
-      </c>
-      <c r="B206" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C206" s="3"/>
+      <c r="A206" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B206" s="3">
+        <v>2</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>740</v>
+      </c>
       <c r="D206" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="E206" s="3"/>
-      <c r="F206" s="71">
-        <v>41676</v>
-      </c>
+      <c r="E206" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="F206" s="71"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A207" s="5" t="s">
-        <v>781</v>
+      <c r="A207" s="3" t="s">
+        <v>779</v>
       </c>
       <c r="B207" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C207" s="3" t="s">
         <v>740</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>741</v>
+        <v>502</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>782</v>
+        <v>690</v>
       </c>
       <c r="F207" s="71"/>
     </row>
-    <row r="208" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="B208" s="3">
-        <v>1</v>
-      </c>
-      <c r="C208" s="3" t="s">
-        <v>740</v>
-      </c>
+        <v>780</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C208" s="3"/>
       <c r="D208" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="E208" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="F208" s="71"/>
+        <v>502</v>
+      </c>
+      <c r="E208" s="3"/>
+      <c r="F208" s="71">
+        <v>41676</v>
+      </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="5" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B209" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C209" s="3" t="s">
         <v>740</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>784</v>
+        <v>741</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="F209" s="71"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A210" s="5" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B210" s="3">
         <v>1</v>
@@ -24193,22 +24233,22 @@
         <v>784</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="F210" s="71"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="5" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B211" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>740</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>786</v>
@@ -24216,65 +24256,69 @@
       <c r="F211" s="71"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A212" s="5"/>
-      <c r="B212" s="3"/>
-      <c r="C212" s="3"/>
-      <c r="D212" s="3"/>
-      <c r="E212" s="3"/>
+      <c r="A212" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="B212" s="3">
+        <v>1</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>786</v>
+      </c>
       <c r="F212" s="71"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="5" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B213" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="D213" s="3"/>
-      <c r="E213" s="3"/>
+        <v>740</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>786</v>
+      </c>
       <c r="F213" s="71"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A214" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="B214" s="3">
-        <v>1</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>793</v>
-      </c>
+      <c r="A214" s="5"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
       <c r="E214" s="3"/>
       <c r="F214" s="71"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A215" s="3" t="s">
-        <v>794</v>
+      <c r="A215" s="5" t="s">
+        <v>790</v>
       </c>
       <c r="B215" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="D215" s="3" t="s">
-        <v>793</v>
-      </c>
+      <c r="D215" s="3"/>
       <c r="E215" s="3"/>
       <c r="F215" s="71"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A216" s="5" t="s">
-        <v>795</v>
+      <c r="A216" s="3" t="s">
+        <v>792</v>
       </c>
       <c r="B216" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>791</v>
@@ -24287,10 +24331,10 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B217" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>791</v>
@@ -24298,17 +24342,15 @@
       <c r="D217" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="E217" s="3" t="s">
-        <v>797</v>
-      </c>
+      <c r="E217" s="3"/>
       <c r="F217" s="71"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A218" s="3" t="s">
-        <v>798</v>
+      <c r="A218" s="5" t="s">
+        <v>795</v>
       </c>
       <c r="B218" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>791</v>
@@ -24320,118 +24362,116 @@
       <c r="F218" s="71"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A219" s="3"/>
-      <c r="B219" s="3"/>
-      <c r="C219" s="3"/>
-      <c r="D219" s="3"/>
-      <c r="E219" s="3"/>
+      <c r="A219" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B219" s="3">
+        <v>0</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>797</v>
+      </c>
       <c r="F219" s="71"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="B220" s="3"/>
+        <v>798</v>
+      </c>
+      <c r="B220" s="3">
+        <v>0</v>
+      </c>
       <c r="C220" s="3" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="E220" s="3"/>
       <c r="F220" s="71"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A221" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="B221" s="3">
-        <v>2</v>
-      </c>
-      <c r="C221" s="3" t="s">
-        <v>1955</v>
-      </c>
-      <c r="D221" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="E221" s="3" t="s">
-        <v>803</v>
-      </c>
+      <c r="A221" s="3"/>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
+      <c r="E221" s="3"/>
       <c r="F221" s="71"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>510</v>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="B222" s="3"/>
       <c r="C222" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="D222" s="3"/>
-      <c r="E222" s="3" t="s">
-        <v>806</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="E222" s="3"/>
       <c r="F222" s="71"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B223" s="3">
         <v>2</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>800</v>
+        <v>1954</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="F223" s="71"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="B224" s="3">
-        <v>1</v>
+        <v>804</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>810</v>
-      </c>
+        <v>805</v>
+      </c>
+      <c r="D224" s="3"/>
       <c r="E224" s="3" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="F224" s="71"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B225" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>800</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>405</v>
+        <v>808</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="F225" s="71"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B226" s="3">
         <v>1</v>
@@ -24440,7 +24480,7 @@
         <v>800</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>811</v>
@@ -24449,7 +24489,7 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B227" s="3">
         <v>1</v>
@@ -24458,16 +24498,16 @@
         <v>800</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>814</v>
+        <v>405</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="F227" s="71"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B228" s="3">
         <v>1</v>
@@ -24479,99 +24519,99 @@
         <v>814</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="F228" s="71"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B229" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>800</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>640</v>
+        <v>814</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>598</v>
+        <v>816</v>
       </c>
       <c r="F229" s="71"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>820</v>
+        <v>817</v>
+      </c>
+      <c r="B230" s="3">
+        <v>1</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>800</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="E230" s="3"/>
+        <v>814</v>
+      </c>
+      <c r="E230" s="3" t="s">
+        <v>816</v>
+      </c>
       <c r="F230" s="71"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A231" s="3"/>
-      <c r="B231" s="3"/>
-      <c r="C231" s="3"/>
-      <c r="D231" s="3"/>
-      <c r="E231" s="3"/>
+      <c r="A231" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B231" s="3">
+        <v>3</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>598</v>
+      </c>
       <c r="F231" s="71"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="B232" s="3">
-        <v>1</v>
+        <v>819</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>820</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="D232" s="3"/>
-      <c r="E232" s="3" t="s">
-        <v>652</v>
-      </c>
+        <v>800</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="E232" s="3"/>
       <c r="F232" s="71"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A233" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="B233" s="3">
-        <v>9</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>652</v>
-      </c>
+      <c r="A233" s="3"/>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
+      <c r="E233" s="3"/>
       <c r="F233" s="71"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B234" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>823</v>
-      </c>
+      <c r="D234" s="3"/>
       <c r="E234" s="3" t="s">
         <v>652</v>
       </c>
@@ -24579,10 +24619,10 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B235" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>805</v>
@@ -24597,10 +24637,10 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B236" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>805</v>
@@ -24615,13 +24655,13 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B237" s="3">
         <v>1</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>856</v>
+        <v>805</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>823</v>
@@ -24633,10 +24673,10 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B238" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>805</v>
@@ -24651,15 +24691,17 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B239" s="3">
         <v>1</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="D239" s="3"/>
+        <v>856</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>823</v>
+      </c>
       <c r="E239" s="3" t="s">
         <v>652</v>
       </c>
@@ -24667,15 +24709,17 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B240" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D240" s="3"/>
+      <c r="D240" s="3" t="s">
+        <v>823</v>
+      </c>
       <c r="E240" s="3" t="s">
         <v>652</v>
       </c>
@@ -24683,10 +24727,10 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B241" s="3">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>805</v>
@@ -24699,10 +24743,10 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B242" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>805</v>
@@ -24715,10 +24759,10 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B243" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>805</v>
@@ -24731,10 +24775,10 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B244" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>805</v>
@@ -24747,10 +24791,10 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B245" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>805</v>
@@ -24763,10 +24807,10 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B246" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>805</v>
@@ -24778,60 +24822,58 @@
       <c r="F246" s="71"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A247" s="3"/>
-      <c r="B247" s="3"/>
-      <c r="C247" s="3"/>
+      <c r="A247" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B247" s="3">
+        <v>1</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>805</v>
+      </c>
       <c r="D247" s="3"/>
-      <c r="E247" s="3"/>
+      <c r="E247" s="3" t="s">
+        <v>652</v>
+      </c>
       <c r="F247" s="71"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
+      </c>
+      <c r="B248" s="3">
+        <v>2</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>839</v>
-      </c>
+      <c r="D248" s="3"/>
       <c r="E248" s="3" t="s">
-        <v>840</v>
+        <v>652</v>
       </c>
       <c r="F248" s="71"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A249" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="B249" s="3">
-        <v>30</v>
-      </c>
-      <c r="C249" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="E249" s="3" t="s">
-        <v>840</v>
-      </c>
+      <c r="A249" s="3"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3"/>
+      <c r="E249" s="3"/>
       <c r="F249" s="71"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="B250" s="3">
-        <v>1</v>
+        <v>837</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>838</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D250" s="3"/>
+      <c r="D250" s="3" t="s">
+        <v>839</v>
+      </c>
       <c r="E250" s="3" t="s">
         <v>840</v>
       </c>
@@ -24839,15 +24881,17 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B251" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D251" s="3"/>
+      <c r="D251" s="3" t="s">
+        <v>842</v>
+      </c>
       <c r="E251" s="3" t="s">
         <v>840</v>
       </c>
@@ -24855,10 +24899,10 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>845</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>510</v>
+        <v>843</v>
+      </c>
+      <c r="B252" s="3">
+        <v>1</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>805</v>
@@ -24871,10 +24915,10 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B253" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>805</v>
@@ -24887,10 +24931,10 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="B254" s="3">
-        <v>2</v>
+        <v>845</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>805</v>
@@ -24902,51 +24946,51 @@
       <c r="F254" s="71"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A255" s="3"/>
-      <c r="B255" s="3"/>
-      <c r="C255" s="3"/>
+      <c r="A255" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="B255" s="3">
+        <v>2</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>805</v>
+      </c>
       <c r="D255" s="3"/>
-      <c r="E255" s="3"/>
+      <c r="E255" s="3" t="s">
+        <v>840</v>
+      </c>
       <c r="F255" s="71"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B256" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>805</v>
       </c>
       <c r="D256" s="3"/>
       <c r="E256" s="3" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="F256" s="71"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A257" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>805</v>
-      </c>
+      <c r="A257" s="3"/>
+      <c r="B257" s="3"/>
+      <c r="C257" s="3"/>
       <c r="D257" s="3"/>
-      <c r="E257" s="3" t="s">
-        <v>849</v>
-      </c>
+      <c r="E257" s="3"/>
       <c r="F257" s="71"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="B258" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>805</v>
@@ -24959,72 +25003,68 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>852</v>
-      </c>
-      <c r="B259" s="3">
-        <v>10</v>
+        <v>850</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="D259" s="3" t="s">
-        <v>853</v>
-      </c>
+      <c r="D259" s="3"/>
       <c r="E259" s="3" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F259" s="71"/>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A260" s="3"/>
-      <c r="B260" s="3"/>
-      <c r="C260" s="3"/>
+      <c r="A260" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="B260" s="3">
+        <v>11</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>805</v>
+      </c>
       <c r="D260" s="3"/>
-      <c r="E260" s="3"/>
+      <c r="E260" s="3" t="s">
+        <v>849</v>
+      </c>
       <c r="F260" s="71"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="B261" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>856</v>
+        <v>805</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>541</v>
+        <v>854</v>
       </c>
       <c r="F261" s="71"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A262" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="B262" s="3">
-        <v>8</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="E262" s="3" t="s">
-        <v>541</v>
-      </c>
+      <c r="A262" s="3"/>
+      <c r="B262" s="3"/>
+      <c r="C262" s="3"/>
+      <c r="D262" s="3"/>
+      <c r="E262" s="3"/>
       <c r="F262" s="71"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B263" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>856</v>
@@ -25039,7 +25079,7 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B264" s="3">
         <v>8</v>
@@ -25057,10 +25097,10 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B265" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>856</v>
@@ -25075,10 +25115,10 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B266" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>856</v>
@@ -25093,10 +25133,10 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B267" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>856</v>
@@ -25107,16 +25147,14 @@
       <c r="E267" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="F267" s="71">
-        <v>41153</v>
-      </c>
+      <c r="F267" s="71"/>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="B268" s="83">
-        <v>16</v>
+        <v>862</v>
+      </c>
+      <c r="B268" s="3">
+        <v>3</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>856</v>
@@ -25127,13 +25165,11 @@
       <c r="E268" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="F268" s="71">
-        <v>41153</v>
-      </c>
+      <c r="F268" s="71"/>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B269" s="3">
         <v>9</v>
@@ -25153,10 +25189,10 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="B270" s="3">
-        <v>9</v>
+        <v>864</v>
+      </c>
+      <c r="B270" s="75">
+        <v>16</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>856</v>
@@ -25173,7 +25209,7 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B271" s="3">
         <v>9</v>
@@ -25193,19 +25229,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B272" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>856</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>870</v>
+        <v>541</v>
       </c>
       <c r="F272" s="71">
         <v>41153</v>
@@ -25213,19 +25249,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B273" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>856</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>870</v>
+        <v>541</v>
       </c>
       <c r="F273" s="71">
         <v>41153</v>
@@ -25233,10 +25269,10 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B274" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>856</v>
@@ -25253,10 +25289,10 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B275" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>856</v>
@@ -25264,23 +25300,25 @@
       <c r="D275" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="E275" s="3"/>
+      <c r="E275" s="3" t="s">
+        <v>870</v>
+      </c>
       <c r="F275" s="71">
-        <v>43132</v>
+        <v>41153</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B276" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>856</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>870</v>
@@ -25291,30 +25329,28 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="B277" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C277" s="3" t="s">
         <v>856</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="E277" s="3" t="s">
-        <v>870</v>
-      </c>
+        <v>869</v>
+      </c>
+      <c r="E277" s="3"/>
       <c r="F277" s="71">
-        <v>41153</v>
+        <v>43132</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B278" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>856</v>
@@ -25325,14 +25361,16 @@
       <c r="E278" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="F278" s="71"/>
+      <c r="F278" s="71">
+        <v>41153</v>
+      </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B279" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>856</v>
@@ -25343,14 +25381,16 @@
       <c r="E279" s="3" t="s">
         <v>870</v>
       </c>
-      <c r="F279" s="71"/>
+      <c r="F279" s="71">
+        <v>41153</v>
+      </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B280" s="3">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>856</v>
@@ -25365,10 +25405,10 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B281" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>856</v>
@@ -25383,88 +25423,88 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B282" s="3">
-        <v>8</v>
-      </c>
-      <c r="C282" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>856</v>
+      </c>
       <c r="D282" s="3" t="s">
-        <v>882</v>
-      </c>
-      <c r="E282" s="3"/>
-      <c r="F282" s="71" t="s">
-        <v>883</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="F282" s="71"/>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A283" s="3"/>
-      <c r="B283" s="3"/>
-      <c r="C283" s="3"/>
-      <c r="D283" s="3"/>
-      <c r="E283" s="3"/>
+      <c r="A283" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="B283" s="3">
+        <v>11</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="E283" s="3" t="s">
+        <v>870</v>
+      </c>
       <c r="F283" s="71"/>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="C284" s="3" t="s">
-        <v>856</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="B284" s="3">
+        <v>8</v>
+      </c>
+      <c r="C284" s="3"/>
       <c r="D284" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="E284" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="F284" s="71"/>
+        <v>882</v>
+      </c>
+      <c r="E284" s="3"/>
+      <c r="F284" s="71" t="s">
+        <v>883</v>
+      </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A285" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="B285" s="3">
-        <v>12</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>856</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="E285" s="3" t="s">
-        <v>888</v>
-      </c>
+      <c r="A285" s="3"/>
+      <c r="B285" s="3"/>
+      <c r="C285" s="3"/>
+      <c r="D285" s="3"/>
+      <c r="E285" s="3"/>
       <c r="F285" s="71"/>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="B286" s="3">
-        <v>6</v>
+        <v>884</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>856</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F286" s="71"/>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="B287" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C287" s="3" t="s">
         <v>856</v>
@@ -25479,10 +25519,10 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B288" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>856</v>
@@ -25497,7 +25537,7 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B289" s="3">
         <v>10</v>
@@ -25515,10 +25555,10 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B290" s="3">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>856</v>
@@ -25533,10 +25573,10 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B291" s="3">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>856</v>
@@ -25550,138 +25590,144 @@
       <c r="F291" s="71"/>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A292" s="3"/>
-      <c r="B292" s="3"/>
-      <c r="C292" s="3"/>
-      <c r="D292" s="3"/>
-      <c r="E292" s="3"/>
+      <c r="A292" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="B292" s="3">
+        <v>33</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="E292" s="3" t="s">
+        <v>888</v>
+      </c>
       <c r="F292" s="71"/>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B293" s="3">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>896</v>
+        <v>856</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>897</v>
+        <v>875</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="F293" s="71">
-        <v>41334</v>
-      </c>
+        <v>888</v>
+      </c>
+      <c r="F293" s="71"/>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A294" s="3" t="s">
-        <v>899</v>
-      </c>
-      <c r="B294" s="3">
-        <v>10</v>
-      </c>
-      <c r="C294" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>897</v>
-      </c>
-      <c r="E294" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="F294" s="71">
-        <v>42887</v>
-      </c>
+      <c r="A294" s="3"/>
+      <c r="B294" s="3"/>
+      <c r="C294" s="3"/>
+      <c r="D294" s="3"/>
+      <c r="E294" s="3"/>
+      <c r="F294" s="71"/>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="B295" s="3"/>
+        <v>895</v>
+      </c>
+      <c r="B295" s="3">
+        <v>9</v>
+      </c>
       <c r="C295" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="D295" s="3"/>
+      <c r="D295" s="3" t="s">
+        <v>897</v>
+      </c>
       <c r="E295" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="F295" s="71"/>
+        <v>898</v>
+      </c>
+      <c r="F295" s="71">
+        <v>41334</v>
+      </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="B296" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>904</v>
-      </c>
-      <c r="F296" s="71"/>
+        <v>898</v>
+      </c>
+      <c r="F296" s="71">
+        <v>42887</v>
+      </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="B297" s="3">
-        <v>7</v>
-      </c>
+        <v>900</v>
+      </c>
+      <c r="B297" s="3"/>
       <c r="C297" s="3" t="s">
         <v>896</v>
       </c>
-      <c r="D297" s="3" t="s">
-        <v>906</v>
-      </c>
+      <c r="D297" s="3"/>
       <c r="E297" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="F297" s="71">
-        <v>42887</v>
-      </c>
+        <v>901</v>
+      </c>
+      <c r="F297" s="71"/>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A298" s="3"/>
-      <c r="B298" s="3"/>
-      <c r="C298" s="3"/>
-      <c r="D298" s="3"/>
-      <c r="E298" s="3"/>
+      <c r="A298" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="B298" s="3">
+        <v>1</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>904</v>
+      </c>
       <c r="F298" s="71"/>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B299" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>576</v>
+        <v>906</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>904</v>
-      </c>
-      <c r="F299" s="71" t="s">
-        <v>883</v>
+        <v>907</v>
+      </c>
+      <c r="F299" s="71">
+        <v>42887</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A300" s="3"/>
-      <c r="B300" s="3">
-        <v>4</v>
-      </c>
+      <c r="B300" s="3"/>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -25689,52 +25735,46 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B301" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>910</v>
+        <v>576</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="F301" s="71"/>
+      <c r="F301" s="71" t="s">
+        <v>883</v>
+      </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A302" s="3" t="s">
-        <v>911</v>
-      </c>
+      <c r="A302" s="3"/>
       <c r="B302" s="3">
-        <v>9</v>
-      </c>
-      <c r="C302" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="E302" s="3" t="s">
-        <v>904</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C302" s="3"/>
+      <c r="D302" s="3"/>
+      <c r="E302" s="3"/>
       <c r="F302" s="71"/>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B303" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>576</v>
+        <v>910</v>
       </c>
       <c r="E303" s="3" t="s">
         <v>904</v>
@@ -25743,10 +25783,10 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="B304" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>896</v>
@@ -25761,10 +25801,10 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="B305" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>896</v>
@@ -25779,10 +25819,10 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B306" s="3">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>896</v>
@@ -25797,16 +25837,16 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="B307" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>917</v>
+        <v>576</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>904</v>
@@ -25815,16 +25855,16 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B308" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>917</v>
+        <v>576</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>904</v>
@@ -25833,10 +25873,10 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B309" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>896</v>
@@ -25851,10 +25891,10 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B310" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>896</v>
@@ -25869,10 +25909,10 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B311" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>896</v>
@@ -25887,10 +25927,10 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B312" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>896</v>
@@ -25898,15 +25938,17 @@
       <c r="D312" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="E312" s="3"/>
+      <c r="E312" s="3" t="s">
+        <v>904</v>
+      </c>
       <c r="F312" s="71"/>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B313" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>896</v>
@@ -25921,52 +25963,50 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B314" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="E314" s="3" t="s">
-        <v>840</v>
-      </c>
+        <v>917</v>
+      </c>
+      <c r="E314" s="3"/>
       <c r="F314" s="71"/>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B315" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>840</v>
+        <v>904</v>
       </c>
       <c r="F315" s="71"/>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="B316" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>926</v>
+        <v>576</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>840</v>
@@ -25975,10 +26015,10 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B317" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>896</v>
@@ -25993,10 +26033,10 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="B318" s="3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>896</v>
@@ -26011,10 +26051,10 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="B319" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>896</v>
@@ -26029,16 +26069,16 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B320" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>576</v>
+        <v>926</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>840</v>
@@ -26047,28 +26087,28 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B321" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>896</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>576</v>
+        <v>926</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>840</v>
       </c>
       <c r="F321" s="71"/>
     </row>
-    <row r="322" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
-        <v>862</v>
+        <v>931</v>
       </c>
       <c r="B322" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>896</v>
@@ -26081,12 +26121,12 @@
       </c>
       <c r="F322" s="71"/>
     </row>
-    <row r="323" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>1956</v>
+        <v>932</v>
       </c>
       <c r="B323" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>896</v>
@@ -26099,30 +26139,41 @@
       </c>
       <c r="F323" s="71"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A324" s="3"/>
-      <c r="B324" s="3"/>
-      <c r="C324" s="3"/>
-      <c r="D324" s="3"/>
-      <c r="E324" s="3"/>
+    <row r="324" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A324" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="B324" s="3">
+        <v>3</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E324" s="3" t="s">
+        <v>840</v>
+      </c>
       <c r="F324" s="71"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>933</v>
+        <v>1955</v>
       </c>
       <c r="B325" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>935</v>
+        <v>896</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="F325" s="71" t="s">
-        <v>598</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="F325" s="71"/>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A326" s="3"/>
@@ -26134,101 +26185,102 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B327" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="E327" s="3"/>
-      <c r="F327" s="71"/>
+        <v>934</v>
+      </c>
+      <c r="F327" s="71" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A328" s="3" t="s">
-        <v>938</v>
-      </c>
-      <c r="B328" s="3">
-        <v>1</v>
-      </c>
-      <c r="C328" s="3" t="s">
-        <v>937</v>
-      </c>
-      <c r="D328" s="3" t="s">
-        <v>633</v>
-      </c>
+      <c r="A328" s="3"/>
+      <c r="B328" s="3"/>
+      <c r="C328" s="3"/>
+      <c r="D328" s="3"/>
       <c r="E328" s="3"/>
       <c r="F328" s="71"/>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A329" s="3"/>
-      <c r="B329" s="3"/>
-      <c r="C329" s="3"/>
-      <c r="D329" s="3"/>
+      <c r="A329" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="B329" s="3">
+        <v>2</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>633</v>
+      </c>
       <c r="E329" s="3"/>
       <c r="F329" s="71"/>
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B330" s="3">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>1957</v>
-      </c>
-      <c r="D330" s="3"/>
+        <v>937</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>633</v>
+      </c>
       <c r="E330" s="3"/>
       <c r="F330" s="71"/>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A331" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="B331" s="3">
-        <v>3</v>
-      </c>
+      <c r="A331" s="3"/>
+      <c r="B331" s="3"/>
+      <c r="C331" s="3"/>
       <c r="D331" s="3"/>
-      <c r="E331" s="3" t="s">
-        <v>1877</v>
-      </c>
+      <c r="E331" s="3"/>
       <c r="F331" s="71"/>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B332" s="3">
-        <v>4</v>
-      </c>
-      <c r="C332" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>1956</v>
+      </c>
       <c r="D332" s="3"/>
       <c r="E332" s="3"/>
       <c r="F332" s="71"/>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B333" s="3">
-        <v>5</v>
-      </c>
-      <c r="C333" s="3"/>
+        <v>3</v>
+      </c>
       <c r="D333" s="3"/>
-      <c r="E333" s="3"/>
+      <c r="E333" s="3" t="s">
+        <v>1877</v>
+      </c>
       <c r="F333" s="71"/>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B334" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
@@ -26236,162 +26288,170 @@
       <c r="F334" s="71"/>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A335" s="3"/>
-      <c r="B335" s="3"/>
+      <c r="A335" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="B335" s="3">
+        <v>5</v>
+      </c>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="3"/>
       <c r="F335" s="71"/>
     </row>
-    <row r="336" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
-        <v>1958</v>
+        <v>943</v>
       </c>
       <c r="B336" s="3">
-        <v>7</v>
-      </c>
-      <c r="C336" s="3" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D336" s="3" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E336" s="3" t="s">
-        <v>1961</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C336" s="3"/>
+      <c r="D336" s="3"/>
+      <c r="E336" s="3"/>
       <c r="F336" s="71"/>
     </row>
-    <row r="337" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
-      <c r="A337" s="3" t="s">
-        <v>1963</v>
-      </c>
-      <c r="B337" s="3">
-        <v>2</v>
-      </c>
-      <c r="C337" s="3" t="s">
-        <v>1959</v>
-      </c>
-      <c r="D337" s="3" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E337" s="3" t="s">
-        <v>1961</v>
-      </c>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A337" s="3"/>
+      <c r="B337" s="3"/>
+      <c r="C337" s="3"/>
+      <c r="D337" s="3"/>
+      <c r="E337" s="3"/>
       <c r="F337" s="71"/>
     </row>
     <row r="338" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
-        <v>1964</v>
-      </c>
-      <c r="B338" s="3" t="s">
-        <v>1966</v>
+        <v>1957</v>
+      </c>
+      <c r="B338" s="3">
+        <v>7</v>
       </c>
       <c r="C338" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D338" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="D338" s="3" t="s">
+      <c r="E338" s="3" t="s">
         <v>1960</v>
-      </c>
-      <c r="E338" s="3" t="s">
-        <v>1962</v>
       </c>
       <c r="F338" s="71"/>
     </row>
     <row r="339" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>1965</v>
-      </c>
-      <c r="B339" s="3" t="s">
-        <v>1966</v>
+        <v>1962</v>
+      </c>
+      <c r="B339" s="3">
+        <v>2</v>
       </c>
       <c r="C339" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D339" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="D339" s="3" t="s">
+      <c r="E339" s="3" t="s">
         <v>1960</v>
-      </c>
-      <c r="E339" s="3" t="s">
-        <v>1962</v>
       </c>
       <c r="F339" s="71"/>
     </row>
     <row r="340" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
-        <v>1967</v>
-      </c>
-      <c r="B340" s="3">
-        <v>2</v>
+        <v>1963</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>1965</v>
       </c>
       <c r="C340" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D340" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="D340" s="3" t="s">
-        <v>1960</v>
-      </c>
       <c r="E340" s="3" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="F340" s="71"/>
     </row>
     <row r="341" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>1968</v>
+        <v>1964</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>1965</v>
       </c>
       <c r="C341" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D341" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="D341" s="3" t="s">
-        <v>1969</v>
-      </c>
       <c r="E341" s="3" t="s">
-        <v>1971</v>
+        <v>1961</v>
       </c>
       <c r="F341" s="71"/>
     </row>
     <row r="342" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
-        <v>1974</v>
+        <v>1966</v>
+      </c>
+      <c r="B342" s="3">
+        <v>2</v>
       </c>
       <c r="C342" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D342" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="D342" s="3" t="s">
-        <v>1970</v>
-      </c>
       <c r="E342" s="3" t="s">
-        <v>1972</v>
+        <v>1961</v>
       </c>
       <c r="F342" s="71"/>
     </row>
     <row r="343" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>1975</v>
+        <v>1967</v>
       </c>
       <c r="C343" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="E343" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F343" s="71"/>
+    </row>
+    <row r="344" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A344" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C344" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E344" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F344" s="71"/>
+    </row>
+    <row r="345" spans="1:6" s="3" customFormat="1" ht="13.2" x14ac:dyDescent="0.3">
+      <c r="A345" s="3" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D345" s="3" t="s">
         <v>1959</v>
       </c>
-      <c r="D343" s="3" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E343" s="3" t="s">
-        <v>1973</v>
-      </c>
-      <c r="F343" s="71"/>
-    </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A344" s="3"/>
-      <c r="B344" s="3"/>
-      <c r="C344" s="3"/>
-      <c r="D344" s="3"/>
-      <c r="E344" s="3"/>
-      <c r="F344" s="71"/>
-    </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A345" s="3"/>
-      <c r="B345" s="3"/>
-      <c r="C345" s="3"/>
-      <c r="D345" s="3"/>
-      <c r="E345" s="3"/>
+      <c r="E345" s="3" t="s">
+        <v>1972</v>
+      </c>
       <c r="F345" s="71"/>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.3">
@@ -27875,9 +27935,19 @@
       <c r="F530" s="71"/>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A531" s="3"/>
+      <c r="B531" s="3"/>
+      <c r="C531" s="3"/>
+      <c r="D531" s="3"/>
+      <c r="E531" s="3"/>
       <c r="F531" s="71"/>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A532" s="3"/>
+      <c r="B532" s="3"/>
+      <c r="C532" s="3"/>
+      <c r="D532" s="3"/>
+      <c r="E532" s="3"/>
       <c r="F532" s="71"/>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.3">
@@ -28262,12 +28332,18 @@
       <c r="F659" s="71"/>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A660" s="60"/>
-      <c r="B660" s="60"/>
-      <c r="C660" s="60"/>
-      <c r="D660" s="60"/>
-      <c r="E660" s="60"/>
-      <c r="F660" s="73"/>
+      <c r="F660" s="71"/>
+    </row>
+    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F661" s="71"/>
+    </row>
+    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A662" s="60"/>
+      <c r="B662" s="60"/>
+      <c r="C662" s="60"/>
+      <c r="D662" s="60"/>
+      <c r="E662" s="60"/>
+      <c r="F662" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -28297,14 +28373,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="77"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="94"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -30712,14 +30788,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -32986,14 +33062,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="77"/>
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="94"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -34722,14 +34798,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -37414,14 +37490,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -41320,14 +41396,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -44624,14 +44700,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="80"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">

--- a/Inventaire du laboratoire de physique-chimie.xlsx
+++ b/Inventaire du laboratoire de physique-chimie.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70470CC-7CF6-42D5-9CAA-A3B80395D089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D101" sheetId="1" r:id="rId1"/>
@@ -6794,6 +6794,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6811,15 +6829,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6841,15 +6850,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9210,297 +9210,6 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
         <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
@@ -9782,6 +9491,297 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9982,15 +9982,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3BCF4F79-2011-4C30-8045-EA1FB6B563C4}" name="Tableau5" displayName="Tableau5" ref="A3:F260" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3BCF4F79-2011-4C30-8045-EA1FB6B563C4}" name="Tableau5" displayName="Tableau5" ref="A3:F260" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
   <autoFilter ref="A3:F260" xr:uid="{3BCF4F79-2011-4C30-8045-EA1FB6B563C4}"/>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{B76C951A-EEC1-4572-844B-27256CE1651B}" name="Désignation du matériel" dataDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{D0B194B0-1DCA-437D-9FAB-7D0DA3265400}" name="Quantité" dataDxfId="106"/>
-    <tableColumn id="4" xr3:uid="{F7F8C1C1-E0C8-495B-BCDC-FFBB05A6CC7F}" name="Lieu de rangement" dataDxfId="105"/>
-    <tableColumn id="5" xr3:uid="{3A8F0D0B-4F23-4303-9931-FFA357C894EA}" name="Discipline / Type de matériel" dataDxfId="104"/>
-    <tableColumn id="6" xr3:uid="{68BE1830-CC53-4201-96D9-AB40F5A1017C}" name="Commentaires" dataDxfId="103"/>
-    <tableColumn id="7" xr3:uid="{EB8982EC-F961-4AE8-9AC0-71A15EE9707F}" name="Date d'arrivée" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{B76C951A-EEC1-4572-844B-27256CE1651B}" name="Désignation du matériel" dataDxfId="96"/>
+    <tableColumn id="3" xr3:uid="{D0B194B0-1DCA-437D-9FAB-7D0DA3265400}" name="Quantité" dataDxfId="95"/>
+    <tableColumn id="4" xr3:uid="{F7F8C1C1-E0C8-495B-BCDC-FFBB05A6CC7F}" name="Lieu de rangement" dataDxfId="94"/>
+    <tableColumn id="5" xr3:uid="{3A8F0D0B-4F23-4303-9931-FFA357C894EA}" name="Discipline / Type de matériel" dataDxfId="93"/>
+    <tableColumn id="6" xr3:uid="{68BE1830-CC53-4201-96D9-AB40F5A1017C}" name="Commentaires" dataDxfId="92"/>
+    <tableColumn id="7" xr3:uid="{EB8982EC-F961-4AE8-9AC0-71A15EE9707F}" name="Date d'arrivée" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10012,15 +10012,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0964DE04-A464-4ADD-BC3D-A26CF0A97D1C}" name="Tableau6" displayName="Tableau6" ref="A3:F662" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{0964DE04-A464-4ADD-BC3D-A26CF0A97D1C}" name="Tableau6" displayName="Tableau6" ref="A3:F662" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
   <autoFilter ref="A3:F662" xr:uid="{0964DE04-A464-4ADD-BC3D-A26CF0A97D1C}"/>
   <tableColumns count="6">
-    <tableColumn id="2" xr3:uid="{F42773BF-2C54-47EC-87D0-205B538A5AE0}" name="Désignation du matériel" dataDxfId="96"/>
-    <tableColumn id="3" xr3:uid="{78BBA9E6-CB04-473D-B15F-DDB0F0CF0F61}" name="Quantité" dataDxfId="95"/>
-    <tableColumn id="4" xr3:uid="{DA63782B-5A3E-481F-AA25-6668F842E120}" name="Lieu de rangement" dataDxfId="94"/>
-    <tableColumn id="5" xr3:uid="{5BF56EFC-5293-44B8-A4CF-B2E433091446}" name="Discipline / Type de matériel" dataDxfId="93"/>
-    <tableColumn id="6" xr3:uid="{FE0A3385-08A1-4311-9770-24637CEC5106}" name="Commentaires" dataDxfId="92"/>
-    <tableColumn id="7" xr3:uid="{37ACA3EB-3A9A-479A-895F-D5CA91324EC0}" name="Date d'arrivée" dataDxfId="91"/>
+    <tableColumn id="2" xr3:uid="{F42773BF-2C54-47EC-87D0-205B538A5AE0}" name="Désignation du matériel" dataDxfId="107"/>
+    <tableColumn id="3" xr3:uid="{78BBA9E6-CB04-473D-B15F-DDB0F0CF0F61}" name="Quantité" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{DA63782B-5A3E-481F-AA25-6668F842E120}" name="Lieu de rangement" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{5BF56EFC-5293-44B8-A4CF-B2E433091446}" name="Discipline / Type de matériel" dataDxfId="104"/>
+    <tableColumn id="6" xr3:uid="{FE0A3385-08A1-4311-9770-24637CEC5106}" name="Commentaires" dataDxfId="103"/>
+    <tableColumn id="7" xr3:uid="{37ACA3EB-3A9A-479A-895F-D5CA91324EC0}" name="Date d'arrivée" dataDxfId="102"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10408,14 +10408,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="I2" s="1" t="s">
@@ -11258,14 +11258,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -12209,116 +12209,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>1096</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="89"/>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="91"/>
+      <c r="A2" s="92"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="76" t="s">
         <v>1097</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="84"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="78"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="76" t="s">
         <v>1975</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="84"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="78"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="s">
+      <c r="A5" s="76" t="s">
         <v>1098</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="84"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="78"/>
     </row>
     <row r="7" spans="1:11" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="88" t="s">
         <v>1099</v>
       </c>
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="88" t="s">
         <v>1100</v>
       </c>
-      <c r="C7" s="85" t="s">
+      <c r="C7" s="88" t="s">
         <v>1101</v>
       </c>
-      <c r="D7" s="85" t="s">
+      <c r="D7" s="88" t="s">
         <v>1102</v>
       </c>
-      <c r="E7" s="87" t="s">
+      <c r="E7" s="90" t="s">
         <v>1103</v>
       </c>
-      <c r="F7" s="80" t="s">
+      <c r="F7" s="86" t="s">
         <v>1109</v>
       </c>
-      <c r="G7" s="76" t="s">
+      <c r="G7" s="82" t="s">
         <v>1104</v>
       </c>
-      <c r="H7" s="77"/>
-      <c r="I7" s="76" t="s">
+      <c r="H7" s="83"/>
+      <c r="I7" s="82" t="s">
         <v>1105</v>
       </c>
-      <c r="J7" s="77"/>
-      <c r="K7" s="78" t="s">
+      <c r="J7" s="83"/>
+      <c r="K7" s="84" t="s">
         <v>1106</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="81"/>
+      <c r="A8" s="89"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="89"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="87"/>
       <c r="G8" s="12" t="s">
         <v>1107</v>
       </c>
@@ -12331,7 +12331,7 @@
       <c r="J8" s="12" t="s">
         <v>1108</v>
       </c>
-      <c r="K8" s="79"/>
+      <c r="K8" s="85"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
@@ -20576,14 +20576,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -28373,14 +28373,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="54" t="s">
@@ -30788,14 +30788,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -33062,14 +33062,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="81"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -34798,14 +34798,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -37490,14 +37490,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -41396,14 +41396,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
@@ -44700,14 +44700,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="84"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="66" t="s">
